--- a/WorkBot/main/data/order_archive/A.L. George/A.L. George_Triphammer_20260515.xlsx
+++ b/WorkBot/main/data/order_archive/A.L. George/A.L. George_Triphammer_20260515.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,33 +566,33 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>77802</t>
+          <t>77221</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ithaca Soda - Ginger Beer</t>
+          <t>Guayaki Yerba Mate - Revel Berry</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>23.95</v>
+        <v>26</v>
       </c>
       <c r="E10" t="n">
-        <v>23.95</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>77801</t>
+          <t>77802</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ithaca Soda - Root Beer</t>
+          <t>Ithaca Soda - Ginger Beer</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -602,6 +602,27 @@
         <v>23.95</v>
       </c>
       <c r="E11" t="n">
+        <v>23.95</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>77801</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ithaca Soda - Root Beer</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>23.95</v>
+      </c>
+      <c r="E12" t="n">
         <v>23.95</v>
       </c>
     </row>
